--- a/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17889072-1866-44D9-B239-EC10100F67AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC66C39-BCA8-4212-A0DB-95A3AA1036CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -357,6 +357,7 @@
       <sheetName val="VINCULO VTS BY SKU OPEN"/>
       <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -364,10 +365,10 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1224</v>
+            <v>1150.5</v>
           </cell>
           <cell r="G4">
-            <v>9.4278283485045522E-2</v>
+            <v>2.8567945383615179E-2</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -375,21 +376,21 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>65</v>
+            <v>115.5</v>
           </cell>
           <cell r="G5">
-            <v>-0.16618075801749266</v>
+            <v>0.48163265306122449</v>
           </cell>
           <cell r="H5" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="6">
           <cell r="F6">
-            <v>469</v>
+            <v>435</v>
           </cell>
           <cell r="G6">
-            <v>-0.14337899543378996</v>
+            <v>-0.20547945205479456</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -397,10 +398,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>62</v>
+            <v>92</v>
           </cell>
           <cell r="G7">
-            <v>-0.36587633658763363</v>
+            <v>-5.9042305904230541E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>BAJO</v>
@@ -408,10 +409,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>6</v>
+            <v>4.5</v>
           </cell>
           <cell r="G8">
-            <v>-0.64032697547683926</v>
+            <v>-0.73024523160762944</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -419,10 +420,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1400</v>
+            <v>1414.5</v>
           </cell>
           <cell r="G9">
-            <v>8.1156978376860422E-2</v>
+            <v>9.2354675652906337E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -430,21 +431,21 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>74</v>
+            <v>139.5</v>
           </cell>
           <cell r="G10">
-            <v>-0.39434523809523814</v>
+            <v>0.1417410714285714</v>
           </cell>
           <cell r="H10" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="11">
           <cell r="F11">
-            <v>239</v>
+            <v>303</v>
           </cell>
           <cell r="G11">
-            <v>-0.21310984735109251</v>
+            <v>-2.3944926668663102E-3</v>
           </cell>
           <cell r="H11" t="str">
             <v>BAJO</v>
@@ -452,10 +453,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>528</v>
+            <v>546.5</v>
           </cell>
           <cell r="G12">
-            <v>-0.202416918429003</v>
+            <v>-0.17447129909365555</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -463,10 +464,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>269</v>
+            <v>364.5</v>
           </cell>
           <cell r="G13">
-            <v>-0.33617498597868767</v>
+            <v>-0.10050476724621427</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -474,10 +475,10 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2798</v>
+            <v>2889</v>
           </cell>
           <cell r="G14">
-            <v>-0.13908896379071622</v>
+            <v>-0.11108935539363085</v>
           </cell>
           <cell r="H14" t="str">
             <v>BAJO</v>
@@ -485,10 +486,10 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1945</v>
+            <v>1814.5</v>
           </cell>
           <cell r="G15">
-            <v>-0.10720247037222497</v>
+            <v>-0.16710482390252046</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -496,10 +497,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1938</v>
+            <v>1791</v>
           </cell>
           <cell r="G16">
-            <v>-0.10383386581469645</v>
+            <v>-0.17180931562132162</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -507,10 +508,10 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2026</v>
+            <v>2175</v>
           </cell>
           <cell r="G17">
-            <v>-0.1574768916696595</v>
+            <v>-9.5514432073795397E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>BAJO</v>
@@ -518,10 +519,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>40</v>
+            <v>69</v>
           </cell>
           <cell r="G18">
-            <v>-0.69955616251280306</v>
+            <v>-0.48173438033458515</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -529,10 +530,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>57</v>
+            <v>138.5</v>
           </cell>
           <cell r="G19">
-            <v>-0.74763533910243507</v>
+            <v>-0.38679814852082917</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -540,10 +541,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>36</v>
+            <v>78</v>
           </cell>
           <cell r="G20">
-            <v>-0.75660725261216966</v>
+            <v>-0.47264904732636759</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -551,10 +552,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>244</v>
+            <v>372</v>
           </cell>
           <cell r="G21">
-            <v>-0.49855207846800553</v>
+            <v>-0.23549743110695931</v>
           </cell>
           <cell r="H21" t="str">
             <v>BAJO</v>
@@ -562,10 +563,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>392</v>
+            <v>592</v>
           </cell>
           <cell r="G22">
-            <v>-0.50779065121853773</v>
+            <v>-0.25666343245248557</v>
           </cell>
           <cell r="H22" t="str">
             <v>BAJO</v>
@@ -584,21 +585,21 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>50</v>
+            <v>35</v>
           </cell>
           <cell r="G24">
-            <v>1.6635859519408491E-2</v>
+            <v>-0.28835489833641403</v>
           </cell>
           <cell r="H24" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>606</v>
+            <v>508</v>
           </cell>
           <cell r="G25">
-            <v>-0.11497610196494956</v>
+            <v>-0.25809877854487517</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -606,10 +607,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>866</v>
+            <v>741</v>
           </cell>
           <cell r="G26">
-            <v>-0.21953217811642289</v>
+            <v>-0.33218630945065741</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -617,10 +618,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>358</v>
+            <v>416</v>
           </cell>
           <cell r="G27">
-            <v>-0.25865963855421692</v>
+            <v>-0.13855421686746994</v>
           </cell>
           <cell r="H27" t="str">
             <v>BAJO</v>
@@ -628,10 +629,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>188</v>
+            <v>213</v>
           </cell>
           <cell r="G28">
-            <v>-0.48691229376007938</v>
+            <v>-0.41868254558987728</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -639,10 +640,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>84</v>
+            <v>105</v>
           </cell>
           <cell r="G29">
-            <v>-0.21528662420382172</v>
+            <v>-1.9108280254777066E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>BAJO</v>
@@ -650,10 +651,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>50</v>
+            <v>54.5</v>
           </cell>
           <cell r="G30">
-            <v>-0.59198813056379818</v>
+            <v>-0.55526706231454004</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -661,10 +662,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>370</v>
+            <v>434.5</v>
           </cell>
           <cell r="G31">
-            <v>-0.53207633938836518</v>
+            <v>-0.45050586341687748</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -672,10 +673,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>402</v>
+            <v>527</v>
           </cell>
           <cell r="G32">
-            <v>-0.38300544160736705</v>
+            <v>-0.19115389981861308</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -683,10 +684,10 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>467</v>
+            <v>721.5</v>
           </cell>
           <cell r="G33">
-            <v>-0.44578703204229153</v>
+            <v>-0.14375876577840108</v>
           </cell>
           <cell r="H33" t="str">
             <v>BAJO</v>
@@ -694,10 +695,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>307</v>
+            <v>451.5</v>
           </cell>
           <cell r="G34">
-            <v>-0.46362770012706478</v>
+            <v>-0.21116581956797964</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -705,10 +706,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>43</v>
+            <v>74</v>
           </cell>
           <cell r="G35">
-            <v>-0.7976903336184773</v>
+            <v>-0.65183917878528652</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -716,10 +717,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>315</v>
+            <v>491</v>
           </cell>
           <cell r="G36">
-            <v>8.0786026200873495E-2</v>
+            <v>0.68465377417342488</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -727,10 +728,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>70</v>
+            <v>112.5</v>
           </cell>
           <cell r="G37">
-            <v>-0.81294789262723188</v>
+            <v>-0.69938054172233688</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -738,21 +739,21 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>261</v>
+            <v>287.5</v>
           </cell>
           <cell r="G38">
-            <v>-4.3796835970024928E-2</v>
+            <v>5.3288925895087491E-2</v>
           </cell>
           <cell r="H38" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="39">
           <cell r="F39">
-            <v>1192</v>
+            <v>816</v>
           </cell>
           <cell r="G39">
-            <v>1.8353335495729266</v>
+            <v>0.94096659098280888</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -760,10 +761,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>591</v>
+            <v>448</v>
           </cell>
           <cell r="G40">
-            <v>1.3980081150866837</v>
+            <v>0.81777941718922897</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -771,21 +772,21 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>267</v>
+            <v>247</v>
           </cell>
           <cell r="G41">
-            <v>1.3632441760137892E-2</v>
+            <v>-6.2295081967213228E-2</v>
           </cell>
           <cell r="H41" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="42">
           <cell r="F42">
-            <v>13</v>
+            <v>31.5</v>
           </cell>
           <cell r="G42">
-            <v>-0.73952641165755917</v>
+            <v>-0.36885245901639341</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -793,10 +794,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>230</v>
+            <v>136</v>
           </cell>
           <cell r="G43">
-            <v>1.8963938179736695</v>
+            <v>0.71265025758443046</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -804,10 +805,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>223</v>
+            <v>117.5</v>
           </cell>
           <cell r="G44">
-            <v>5.5066312997347477</v>
+            <v>2.4283819628647216</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -815,13 +816,13 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>19</v>
+            <v>55.5</v>
           </cell>
           <cell r="G45">
-            <v>-0.49333333333333329</v>
+            <v>0.48</v>
           </cell>
           <cell r="H45" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="46">
@@ -837,10 +838,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>1</v>
+            <v>0.5</v>
           </cell>
           <cell r="G47">
-            <v>-0.69444444444444442</v>
+            <v>-0.84722222222222221</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -848,6 +849,7 @@
         </row>
       </sheetData>
       <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1104,11 +1106,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1224</v>
+        <v>1150.5</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>9.4278283485045522E-2</v>
+        <v>2.8567945383615179E-2</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1133,15 +1135,15 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>65</v>
+        <v>115.5</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>-0.16618075801749266</v>
+        <v>0.48163265306122449</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H3">
         <v>1.59</v>
@@ -1162,11 +1164,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.14337899543378996</v>
+        <v>-0.20547945205479456</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1191,11 +1193,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>62</v>
+        <v>92</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-0.36587633658763363</v>
+        <v>-5.9042305904230541E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1220,11 +1222,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>6</v>
+        <v>4.5</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.64032697547683926</v>
+        <v>-0.73024523160762944</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1249,11 +1251,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1400</v>
+        <v>1414.5</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>8.1156978376860422E-2</v>
+        <v>9.2354675652906337E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1278,15 +1280,15 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>74</v>
+        <v>139.5</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>-0.39434523809523814</v>
+        <v>0.1417410714285714</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H8">
         <v>0.63</v>
@@ -1307,11 +1309,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>239</v>
+        <v>303</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-0.21310984735109251</v>
+        <v>-2.3944926668663102E-3</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1336,11 +1338,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>528</v>
+        <v>546.5</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.202416918429003</v>
+        <v>-0.17447129909365555</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1365,11 +1367,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>269</v>
+        <v>364.5</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.33617498597868767</v>
+        <v>-0.10050476724621427</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1394,11 +1396,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2798</v>
+        <v>2889</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.13908896379071622</v>
+        <v>-0.11108935539363085</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1423,11 +1425,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1945</v>
+        <v>1814.5</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.10720247037222497</v>
+        <v>-0.16710482390252046</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1452,11 +1454,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1938</v>
+        <v>1791</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.10383386581469645</v>
+        <v>-0.17180931562132162</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1481,11 +1483,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2026</v>
+        <v>2175</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-0.1574768916696595</v>
+        <v>-9.5514432073795397E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1510,11 +1512,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>40</v>
+        <v>69</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.69955616251280306</v>
+        <v>-0.48173438033458515</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1539,11 +1541,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>57</v>
+        <v>138.5</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.74763533910243507</v>
+        <v>-0.38679814852082917</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1568,11 +1570,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>36</v>
+        <v>78</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.75660725261216966</v>
+        <v>-0.47264904732636759</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1597,11 +1599,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>244</v>
+        <v>372</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.49855207846800553</v>
+        <v>-0.23549743110695931</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1626,11 +1628,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>392</v>
+        <v>592</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.50779065121853773</v>
+        <v>-0.25666343245248557</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1684,15 +1686,15 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>1.6635859519408491E-2</v>
+        <v>-0.28835489833641403</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1713,11 +1715,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>606</v>
+        <v>508</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.11497610196494956</v>
+        <v>-0.25809877854487517</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1742,11 +1744,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>866</v>
+        <v>741</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.21953217811642289</v>
+        <v>-0.33218630945065741</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1771,11 +1773,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>358</v>
+        <v>416</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.25865963855421692</v>
+        <v>-0.13855421686746994</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1800,11 +1802,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>188</v>
+        <v>213</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.48691229376007938</v>
+        <v>-0.41868254558987728</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1829,11 +1831,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>84</v>
+        <v>105</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-0.21528662420382172</v>
+        <v>-1.9108280254777066E-2</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1858,11 +1860,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>50</v>
+        <v>54.5</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.59198813056379818</v>
+        <v>-0.55526706231454004</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1887,11 +1889,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>370</v>
+        <v>434.5</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.53207633938836518</v>
+        <v>-0.45050586341687748</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1916,11 +1918,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>402</v>
+        <v>527</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.38300544160736705</v>
+        <v>-0.19115389981861308</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1945,11 +1947,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>467</v>
+        <v>721.5</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.44578703204229153</v>
+        <v>-0.14375876577840108</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1974,11 +1976,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>307</v>
+        <v>451.5</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.46362770012706478</v>
+        <v>-0.21116581956797964</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2003,11 +2005,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>43</v>
+        <v>74</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.7976903336184773</v>
+        <v>-0.65183917878528652</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2032,11 +2034,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>315</v>
+        <v>491</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>8.0786026200873495E-2</v>
+        <v>0.68465377417342488</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2061,11 +2063,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>70</v>
+        <v>112.5</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.81294789262723188</v>
+        <v>-0.69938054172233688</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2090,15 +2092,15 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>261</v>
+        <v>287.5</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>-4.3796835970024928E-2</v>
+        <v>5.3288925895087491E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H36">
         <v>0.81</v>
@@ -2119,11 +2121,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>1192</v>
+        <v>816</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>1.8353335495729266</v>
+        <v>0.94096659098280888</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2148,11 +2150,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>591</v>
+        <v>448</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>1.3980081150866837</v>
+        <v>0.81777941718922897</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2177,15 +2179,15 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>267</v>
+        <v>247</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>1.3632441760137892E-2</v>
+        <v>-6.2295081967213228E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H39">
         <v>0.81</v>
@@ -2206,11 +2208,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>13</v>
+        <v>31.5</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.73952641165755917</v>
+        <v>-0.36885245901639341</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2235,11 +2237,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>230</v>
+        <v>136</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>1.8963938179736695</v>
+        <v>0.71265025758443046</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2264,11 +2266,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>223</v>
+        <v>117.5</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>5.5066312997347477</v>
+        <v>2.4283819628647216</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2293,15 +2295,15 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>19</v>
+        <v>55.5</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>-0.49333333333333329</v>
+        <v>0.48</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H43">
         <v>2.62</v>
@@ -2351,11 +2353,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.69444444444444442</v>
+        <v>-0.84722222222222221</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3FC66C39-BCA8-4212-A0DB-95A3AA1036CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395DB923-3516-4085-968C-5BFA5106F1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -358,6 +358,7 @@
       <sheetName val="DESV. VTS BY SKU"/>
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -365,10 +366,10 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1150.5</v>
+            <v>1267.6666666666667</v>
           </cell>
           <cell r="G4">
-            <v>2.8567945383615179E-2</v>
+            <v>0.13331707845687046</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -376,10 +377,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>115.5</v>
+            <v>107.66666666666667</v>
           </cell>
           <cell r="G5">
-            <v>0.48163265306122449</v>
+            <v>0.38114674441205065</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -387,10 +388,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>435</v>
+            <v>434.66666666666669</v>
           </cell>
           <cell r="G6">
-            <v>-0.20547945205479456</v>
+            <v>-0.20608828006088276</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -398,21 +399,21 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>92</v>
+            <v>132.33333333333334</v>
           </cell>
           <cell r="G7">
-            <v>-5.9042305904230541E-2</v>
+            <v>0.35347900201456706</v>
           </cell>
           <cell r="H7" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="8">
           <cell r="F8">
-            <v>4.5</v>
+            <v>6.666666666666667</v>
           </cell>
           <cell r="G8">
-            <v>-0.73024523160762944</v>
+            <v>-0.60036330608537702</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -420,10 +421,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1414.5</v>
+            <v>1381</v>
           </cell>
           <cell r="G9">
-            <v>9.2354675652906337E-2</v>
+            <v>6.6484133670317247E-2</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -431,10 +432,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>139.5</v>
+            <v>141.33333333333334</v>
           </cell>
           <cell r="G10">
-            <v>0.1417410714285714</v>
+            <v>0.15674603174603186</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -442,21 +443,21 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>303</v>
+            <v>345.66666666666669</v>
           </cell>
           <cell r="G11">
-            <v>-2.3944926668663102E-3</v>
+            <v>0.13808241045595127</v>
           </cell>
           <cell r="H11" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="12">
           <cell r="F12">
-            <v>546.5</v>
+            <v>661.33333333333337</v>
           </cell>
           <cell r="G12">
-            <v>-0.17447129909365555</v>
+            <v>-1.0070493454178431E-3</v>
           </cell>
           <cell r="H12" t="str">
             <v>BAJO</v>
@@ -464,10 +465,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>364.5</v>
+            <v>396.66666666666669</v>
           </cell>
           <cell r="G13">
-            <v>-0.10050476724621427</v>
+            <v>-2.1125444008225802E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>BAJO</v>
@@ -475,21 +476,21 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>2889</v>
+            <v>3322.3333333333335</v>
           </cell>
           <cell r="G14">
-            <v>-0.11108935539363085</v>
+            <v>2.2242113163918553E-2</v>
           </cell>
           <cell r="H14" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="15">
           <cell r="F15">
-            <v>1814.5</v>
+            <v>2112.3333333333335</v>
           </cell>
           <cell r="G15">
-            <v>-0.16710482390252046</v>
+            <v>-3.0392811439381218E-2</v>
           </cell>
           <cell r="H15" t="str">
             <v>BAJO</v>
@@ -497,10 +498,10 @@
         </row>
         <row r="16">
           <cell r="F16">
-            <v>1791</v>
+            <v>2099.3333333333335</v>
           </cell>
           <cell r="G16">
-            <v>-0.17180931562132162</v>
+            <v>-2.9230424303570368E-2</v>
           </cell>
           <cell r="H16" t="str">
             <v>BAJO</v>
@@ -508,21 +509,21 @@
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2175</v>
+            <v>2440.6666666666665</v>
           </cell>
           <cell r="G17">
-            <v>-9.5514432073795397E-2</v>
+            <v>1.4964494767152559E-2</v>
           </cell>
           <cell r="H17" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="18">
           <cell r="F18">
-            <v>69</v>
+            <v>71</v>
           </cell>
           <cell r="G18">
-            <v>-0.48173438033458515</v>
+            <v>-0.46671218846022533</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -530,10 +531,10 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>138.5</v>
+            <v>207.66666666666666</v>
           </cell>
           <cell r="G19">
-            <v>-0.38679814852082917</v>
+            <v>-8.0566176963842606E-2</v>
           </cell>
           <cell r="H19" t="str">
             <v>BAJO</v>
@@ -541,10 +542,10 @@
         </row>
         <row r="20">
           <cell r="F20">
-            <v>78</v>
+            <v>131.66666666666666</v>
           </cell>
           <cell r="G20">
-            <v>-0.47264904732636759</v>
+            <v>-0.10981356279450938</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -552,24 +553,24 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>372</v>
+            <v>525.33333333333337</v>
           </cell>
           <cell r="G21">
-            <v>-0.23549743110695931</v>
+            <v>7.9620115210960796E-2</v>
           </cell>
           <cell r="H21" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>592</v>
+            <v>811.66666666666663</v>
           </cell>
           <cell r="G22">
-            <v>-0.25666343245248557</v>
+            <v>1.9157962825561592E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="23">
@@ -585,21 +586,21 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>35</v>
+            <v>63.333333333333336</v>
           </cell>
           <cell r="G24">
-            <v>-0.28835489833641403</v>
+            <v>0.28773875539125093</v>
           </cell>
           <cell r="H24" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="25">
           <cell r="F25">
-            <v>508</v>
+            <v>605.66666666666663</v>
           </cell>
           <cell r="G25">
-            <v>-0.25809877854487517</v>
+            <v>-0.11546291379005147</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -607,10 +608,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>741</v>
+            <v>850</v>
           </cell>
           <cell r="G26">
-            <v>-0.33218630945065741</v>
+            <v>-0.23395190692720491</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -618,21 +619,21 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>416</v>
+            <v>576.33333333333337</v>
           </cell>
           <cell r="G27">
-            <v>-0.13855421686746994</v>
+            <v>0.19346134538152615</v>
           </cell>
           <cell r="H27" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="28">
           <cell r="F28">
-            <v>213</v>
+            <v>295</v>
           </cell>
           <cell r="G28">
-            <v>-0.41868254558987728</v>
+            <v>-0.194888971591614</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -640,21 +641,21 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>105</v>
+            <v>131.33333333333334</v>
           </cell>
           <cell r="G29">
-            <v>-1.9108280254777066E-2</v>
+            <v>0.22689313517339005</v>
           </cell>
           <cell r="H29" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="30">
           <cell r="F30">
-            <v>54.5</v>
+            <v>75</v>
           </cell>
           <cell r="G30">
-            <v>-0.55526706231454004</v>
+            <v>-0.38798219584569738</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -662,10 +663,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>434.5</v>
+            <v>440.33333333333331</v>
           </cell>
           <cell r="G31">
-            <v>-0.45050586341687748</v>
+            <v>-0.44312868858741472</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -673,10 +674,10 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>527</v>
+            <v>630</v>
           </cell>
           <cell r="G32">
-            <v>-0.19115389981861308</v>
+            <v>-3.3068229384679682E-2</v>
           </cell>
           <cell r="H32" t="str">
             <v>BAJO</v>
@@ -684,21 +685,21 @@
         </row>
         <row r="33">
           <cell r="F33">
-            <v>721.5</v>
+            <v>866.33333333333337</v>
           </cell>
           <cell r="G33">
-            <v>-0.14375876577840108</v>
+            <v>2.8122415219189456E-2</v>
           </cell>
           <cell r="H33" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>451.5</v>
+            <v>565</v>
           </cell>
           <cell r="G34">
-            <v>-0.21116581956797964</v>
+            <v>-1.2865311308767446E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -706,10 +707,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>74</v>
+            <v>49.333333333333336</v>
           </cell>
           <cell r="G35">
-            <v>-0.65183917878528652</v>
+            <v>-0.76789278585685772</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -717,10 +718,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>491</v>
+            <v>638</v>
           </cell>
           <cell r="G36">
-            <v>0.68465377417342488</v>
+            <v>1.189020586400499</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -728,10 +729,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>112.5</v>
+            <v>163.66666666666666</v>
           </cell>
           <cell r="G37">
-            <v>-0.69938054172233688</v>
+            <v>-0.56265435847605172</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -739,10 +740,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>287.5</v>
+            <v>312.33333333333331</v>
           </cell>
           <cell r="G38">
-            <v>5.3288925895087491E-2</v>
+            <v>0.1442686650013878</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -750,10 +751,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>816</v>
+            <v>689</v>
           </cell>
           <cell r="G39">
-            <v>0.94096659098280888</v>
+            <v>0.63887987890582765</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -761,10 +762,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>448</v>
+            <v>373.66666666666669</v>
           </cell>
           <cell r="G40">
-            <v>0.81777941718922897</v>
+            <v>0.51616869543833754</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -772,10 +773,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>247</v>
+            <v>237.33333333333334</v>
           </cell>
           <cell r="G41">
-            <v>-6.2295081967213228E-2</v>
+            <v>-9.899338510209954E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -783,10 +784,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>31.5</v>
+            <v>49.333333333333336</v>
           </cell>
           <cell r="G42">
-            <v>-0.36885245901639341</v>
+            <v>-1.1536126290224602E-2</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -794,10 +795,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>136</v>
+            <v>117.66666666666667</v>
           </cell>
           <cell r="G43">
-            <v>0.71265025758443046</v>
+            <v>0.48177828658652944</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -805,10 +806,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>117.5</v>
+            <v>95</v>
           </cell>
           <cell r="G44">
-            <v>2.4283819628647216</v>
+            <v>1.7718832891246685</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -816,10 +817,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>55.5</v>
+            <v>55</v>
           </cell>
           <cell r="G45">
-            <v>0.48</v>
+            <v>0.46666666666666656</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -838,10 +839,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>0.5</v>
+            <v>1.6666666666666667</v>
           </cell>
           <cell r="G47">
-            <v>-0.84722222222222221</v>
+            <v>-0.4907407407407407</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -850,6 +851,7 @@
       </sheetData>
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1106,11 +1108,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1150.5</v>
+        <v>1267.6666666666667</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>2.8567945383615179E-2</v>
+        <v>0.13331707845687046</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1135,11 +1137,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>115.5</v>
+        <v>107.66666666666667</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.48163265306122449</v>
+        <v>0.38114674441205065</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1164,11 +1166,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>435</v>
+        <v>434.66666666666669</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.20547945205479456</v>
+        <v>-0.20608828006088276</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1193,15 +1195,15 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>92</v>
+        <v>132.33333333333334</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>-5.9042305904230541E-2</v>
+        <v>0.35347900201456706</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H5">
         <v>3.61</v>
@@ -1222,11 +1224,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>4.5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.73024523160762944</v>
+        <v>-0.60036330608537702</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1251,11 +1253,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1414.5</v>
+        <v>1381</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>9.2354675652906337E-2</v>
+        <v>6.6484133670317247E-2</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1280,11 +1282,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>139.5</v>
+        <v>141.33333333333334</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.1417410714285714</v>
+        <v>0.15674603174603186</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1309,15 +1311,15 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>303</v>
+        <v>345.66666666666669</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>-2.3944926668663102E-3</v>
+        <v>0.13808241045595127</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H9">
         <v>0.63</v>
@@ -1338,11 +1340,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>546.5</v>
+        <v>661.33333333333337</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-0.17447129909365555</v>
+        <v>-1.0070493454178431E-3</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1367,11 +1369,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>364.5</v>
+        <v>396.66666666666669</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-0.10050476724621427</v>
+        <v>-2.1125444008225802E-2</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1396,15 +1398,15 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>2889</v>
+        <v>3322.3333333333335</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>-0.11108935539363085</v>
+        <v>2.2242113163918553E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1425,11 +1427,11 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>1814.5</v>
+        <v>2112.3333333333335</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-0.16710482390252046</v>
+        <v>-3.0392811439381218E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
@@ -1454,11 +1456,11 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>1791</v>
+        <v>2099.3333333333335</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-0.17180931562132162</v>
+        <v>-2.9230424303570368E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
@@ -1483,15 +1485,15 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2175</v>
+        <v>2440.6666666666665</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>-9.5514432073795397E-2</v>
+        <v>1.4964494767152559E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1512,11 +1514,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.48173438033458515</v>
+        <v>-0.46671218846022533</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1541,11 +1543,11 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>138.5</v>
+        <v>207.66666666666666</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-0.38679814852082917</v>
+        <v>-8.0566176963842606E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
@@ -1570,11 +1572,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>78</v>
+        <v>131.66666666666666</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.47264904732636759</v>
+        <v>-0.10981356279450938</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1599,15 +1601,15 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>372</v>
+        <v>525.33333333333337</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>-0.23549743110695931</v>
+        <v>7.9620115210960796E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1628,15 +1630,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>592</v>
+        <v>811.66666666666663</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>-0.25666343245248557</v>
+        <v>1.9157962825561592E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1686,15 +1688,15 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>35</v>
+        <v>63.333333333333336</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>-0.28835489833641403</v>
+        <v>0.28773875539125093</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H22">
         <v>4.1500000000000004</v>
@@ -1715,11 +1717,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>508</v>
+        <v>605.66666666666663</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.25809877854487517</v>
+        <v>-0.11546291379005147</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1744,11 +1746,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>741</v>
+        <v>850</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.33218630945065741</v>
+        <v>-0.23395190692720491</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1773,15 +1775,15 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>416</v>
+        <v>576.33333333333337</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>-0.13855421686746994</v>
+        <v>0.19346134538152615</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H25">
         <v>1.63</v>
@@ -1802,11 +1804,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>213</v>
+        <v>295</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.41868254558987728</v>
+        <v>-0.194888971591614</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1831,15 +1833,15 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>105</v>
+        <v>131.33333333333334</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>-1.9108280254777066E-2</v>
+        <v>0.22689313517339005</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H27">
         <v>6.15</v>
@@ -1860,11 +1862,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>54.5</v>
+        <v>75</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.55526706231454004</v>
+        <v>-0.38798219584569738</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1889,11 +1891,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>434.5</v>
+        <v>440.33333333333331</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.45050586341687748</v>
+        <v>-0.44312868858741472</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1918,11 +1920,11 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>527</v>
+        <v>630</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-0.19115389981861308</v>
+        <v>-3.3068229384679682E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
@@ -1947,15 +1949,15 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>721.5</v>
+        <v>866.33333333333337</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>-0.14375876577840108</v>
+        <v>2.8122415219189456E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H31">
         <v>1.1599999999999999</v>
@@ -1976,11 +1978,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>451.5</v>
+        <v>565</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-0.21116581956797964</v>
+        <v>-1.2865311308767446E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2005,11 +2007,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>74</v>
+        <v>49.333333333333336</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.65183917878528652</v>
+        <v>-0.76789278585685772</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2034,11 +2036,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>491</v>
+        <v>638</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>0.68465377417342488</v>
+        <v>1.189020586400499</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2063,11 +2065,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>112.5</v>
+        <v>163.66666666666666</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.69938054172233688</v>
+        <v>-0.56265435847605172</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2092,11 +2094,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>287.5</v>
+        <v>312.33333333333331</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>5.3288925895087491E-2</v>
+        <v>0.1442686650013878</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2121,11 +2123,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>816</v>
+        <v>689</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.94096659098280888</v>
+        <v>0.63887987890582765</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2150,11 +2152,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>448</v>
+        <v>373.66666666666669</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.81777941718922897</v>
+        <v>0.51616869543833754</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2179,11 +2181,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>247</v>
+        <v>237.33333333333334</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-6.2295081967213228E-2</v>
+        <v>-9.899338510209954E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2208,11 +2210,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>31.5</v>
+        <v>49.333333333333336</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-0.36885245901639341</v>
+        <v>-1.1536126290224602E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2237,11 +2239,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>136</v>
+        <v>117.66666666666667</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.71265025758443046</v>
+        <v>0.48177828658652944</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2266,11 +2268,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>117.5</v>
+        <v>95</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>2.4283819628647216</v>
+        <v>1.7718832891246685</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2295,11 +2297,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>55.5</v>
+        <v>55</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.48</v>
+        <v>0.46666666666666656</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2353,11 +2355,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>0.5</v>
+        <v>1.6666666666666667</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.84722222222222221</v>
+        <v>-0.4907407407407407</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{395DB923-3516-4085-968C-5BFA5106F1C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50AD65E-4D11-4ED0-B390-6B7CE65E64BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -359,6 +359,7 @@
       <sheetName val="INVENTARIO NACIONAL 04-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -366,10 +367,10 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1267.6666666666667</v>
+            <v>1243</v>
           </cell>
           <cell r="G4">
-            <v>0.13331707845687046</v>
+            <v>0.11126462938881665</v>
           </cell>
           <cell r="H4" t="str">
             <v>SUBIÓ</v>
@@ -377,10 +378,10 @@
         </row>
         <row r="5">
           <cell r="F5">
-            <v>107.66666666666667</v>
+            <v>106.25</v>
           </cell>
           <cell r="G5">
-            <v>0.38114674441205065</v>
+            <v>0.36297376093294464</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -388,10 +389,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>434.66666666666669</v>
+            <v>432.5</v>
           </cell>
           <cell r="G6">
-            <v>-0.20608828006088276</v>
+            <v>-0.21004566210045661</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -399,10 +400,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>132.33333333333334</v>
+            <v>116.75</v>
           </cell>
           <cell r="G7">
-            <v>0.35347900201456706</v>
+            <v>0.19409576940957707</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -410,10 +411,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>6.666666666666667</v>
+            <v>10.25</v>
           </cell>
           <cell r="G8">
-            <v>-0.60036330608537702</v>
+            <v>-0.38555858310626712</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -421,10 +422,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1381</v>
+            <v>1435</v>
           </cell>
           <cell r="G9">
-            <v>6.6484133670317247E-2</v>
+            <v>0.10818590283628193</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -432,10 +433,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>141.33333333333334</v>
+            <v>139.25</v>
           </cell>
           <cell r="G10">
-            <v>0.15674603174603186</v>
+            <v>0.13969494047619047</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -443,10 +444,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>345.66666666666669</v>
+            <v>369.25</v>
           </cell>
           <cell r="G11">
-            <v>0.13808241045595127</v>
+            <v>0.2157288237054773</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -454,32 +455,32 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>661.33333333333337</v>
+            <v>807.75</v>
           </cell>
           <cell r="G12">
-            <v>-1.0070493454178431E-3</v>
+            <v>0.220166163141994</v>
           </cell>
           <cell r="H12" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="13">
           <cell r="F13">
-            <v>396.66666666666669</v>
+            <v>454</v>
           </cell>
           <cell r="G13">
-            <v>-2.1125444008225802E-2</v>
+            <v>0.12035894559730775</v>
           </cell>
           <cell r="H13" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3322.3333333333335</v>
+            <v>3508.75</v>
           </cell>
           <cell r="G14">
-            <v>2.2242113163918553E-2</v>
+            <v>7.9600285310694963E-2</v>
           </cell>
           <cell r="H14" t="str">
             <v>SUBIÓ</v>
@@ -487,32 +488,32 @@
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2112.3333333333335</v>
+            <v>2274.5</v>
           </cell>
           <cell r="G15">
-            <v>-3.0392811439381218E-2</v>
+            <v>4.4045234518444332E-2</v>
           </cell>
           <cell r="H15" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2099.3333333333335</v>
+            <v>2225.25</v>
           </cell>
           <cell r="G16">
-            <v>-2.9230424303570368E-2</v>
+            <v>2.8995712123759843E-2</v>
           </cell>
           <cell r="H16" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2440.6666666666665</v>
+            <v>2504.75</v>
           </cell>
           <cell r="G17">
-            <v>1.4964494767152559E-2</v>
+            <v>4.1613897132487754E-2</v>
           </cell>
           <cell r="H17" t="str">
             <v>SUBIÓ</v>
@@ -520,10 +521,10 @@
         </row>
         <row r="18">
           <cell r="F18">
-            <v>71</v>
+            <v>73.5</v>
           </cell>
           <cell r="G18">
-            <v>-0.46671218846022533</v>
+            <v>-0.44793444861727549</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -531,21 +532,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>207.66666666666666</v>
+            <v>230.5</v>
           </cell>
           <cell r="G19">
-            <v>-8.0566176963842606E-2</v>
+            <v>2.0527269068222997E-2</v>
           </cell>
           <cell r="H19" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>131.66666666666666</v>
+            <v>131.5</v>
           </cell>
           <cell r="G20">
-            <v>-0.10981356279450938</v>
+            <v>-0.11094038106945292</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -553,10 +554,10 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>525.33333333333337</v>
+            <v>519.25</v>
           </cell>
           <cell r="G21">
-            <v>7.9620115210960796E-2</v>
+            <v>6.7118169079869228E-2</v>
           </cell>
           <cell r="H21" t="str">
             <v>SUBIÓ</v>
@@ -564,10 +565,10 @@
         </row>
         <row r="22">
           <cell r="F22">
-            <v>811.66666666666663</v>
+            <v>805.25</v>
           </cell>
           <cell r="G22">
-            <v>1.9157962825561592E-2</v>
+            <v>1.1100964556817638E-2</v>
           </cell>
           <cell r="H22" t="str">
             <v>SUBIÓ</v>
@@ -586,10 +587,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>63.333333333333336</v>
+            <v>50.5</v>
           </cell>
           <cell r="G24">
-            <v>0.28773875539125093</v>
+            <v>2.6802218114602594E-2</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -597,10 +598,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>605.66666666666663</v>
+            <v>620.5</v>
           </cell>
           <cell r="G25">
-            <v>-0.11546291379005147</v>
+            <v>-9.3799787573021765E-2</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -608,10 +609,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>850</v>
+            <v>955</v>
           </cell>
           <cell r="G26">
-            <v>-0.23395190692720491</v>
+            <v>-0.13932243660644783</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -619,10 +620,10 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>576.33333333333337</v>
+            <v>548.25</v>
           </cell>
           <cell r="G27">
-            <v>0.19346134538152615</v>
+            <v>0.13530685240963858</v>
           </cell>
           <cell r="H27" t="str">
             <v>SUBIÓ</v>
@@ -630,10 +631,10 @@
         </row>
         <row r="28">
           <cell r="F28">
-            <v>295</v>
+            <v>348.5</v>
           </cell>
           <cell r="G28">
-            <v>-0.194888971591614</v>
+            <v>-4.8877310507381311E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -641,10 +642,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>131.33333333333334</v>
+            <v>127</v>
           </cell>
           <cell r="G29">
-            <v>0.22689313517339005</v>
+            <v>0.18641188959660293</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -652,10 +653,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>75</v>
+            <v>104.75</v>
           </cell>
           <cell r="G30">
-            <v>-0.38798219584569738</v>
+            <v>-0.14521513353115723</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -663,10 +664,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>440.33333333333331</v>
+            <v>391</v>
           </cell>
           <cell r="G31">
-            <v>-0.44312868858741472</v>
+            <v>-0.50551851000229941</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -674,21 +675,21 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>630</v>
+            <v>683.25</v>
           </cell>
           <cell r="G32">
-            <v>-3.3068229384679682E-2</v>
+            <v>4.8660527417329513E-2</v>
           </cell>
           <cell r="H32" t="str">
-            <v>BAJO</v>
+            <v>SUBIÓ</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>866.33333333333337</v>
+            <v>885</v>
           </cell>
           <cell r="G33">
-            <v>2.8122415219189456E-2</v>
+            <v>5.0275110583666072E-2</v>
           </cell>
           <cell r="H33" t="str">
             <v>SUBIÓ</v>
@@ -696,10 +697,10 @@
         </row>
         <row r="34">
           <cell r="F34">
-            <v>565</v>
+            <v>544.5</v>
           </cell>
           <cell r="G34">
-            <v>-1.2865311308767446E-2</v>
+            <v>-4.8681702668360916E-2</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -707,10 +708,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>49.333333333333336</v>
+            <v>42</v>
           </cell>
           <cell r="G35">
-            <v>-0.76789278585685772</v>
+            <v>-0.80239520958083832</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -718,10 +719,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>638</v>
+            <v>693</v>
           </cell>
           <cell r="G36">
-            <v>1.189020586400499</v>
+            <v>1.3777292576419216</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -729,10 +730,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>163.66666666666666</v>
+            <v>159</v>
           </cell>
           <cell r="G37">
-            <v>-0.56265435847605172</v>
+            <v>-0.57512449896756956</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -740,10 +741,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>312.33333333333331</v>
+            <v>300</v>
           </cell>
           <cell r="G38">
-            <v>0.1442686650013878</v>
+            <v>9.9084096586178338E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -751,10 +752,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>689</v>
+            <v>627.25</v>
           </cell>
           <cell r="G39">
-            <v>0.63887987890582765</v>
+            <v>0.49199913504162596</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -762,10 +763,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>373.66666666666669</v>
+            <v>336.75</v>
           </cell>
           <cell r="G40">
-            <v>0.51616869543833754</v>
+            <v>0.3663777203983769</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -773,10 +774,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>237.33333333333334</v>
+            <v>255.25</v>
           </cell>
           <cell r="G41">
-            <v>-9.899338510209954E-2</v>
+            <v>-3.0974978429680888E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -784,10 +785,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>49.333333333333336</v>
+            <v>47.25</v>
           </cell>
           <cell r="G42">
-            <v>-1.1536126290224602E-2</v>
+            <v>-5.3278688524590168E-2</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -795,10 +796,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>117.66666666666667</v>
+            <v>99.75</v>
           </cell>
           <cell r="G43">
-            <v>0.48177828658652944</v>
+            <v>0.25615340583858037</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -806,10 +807,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>95</v>
+            <v>80.5</v>
           </cell>
           <cell r="G44">
-            <v>1.7718832891246685</v>
+            <v>1.3488063660477452</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -817,10 +818,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>55</v>
+            <v>50.25</v>
           </cell>
           <cell r="G45">
-            <v>0.46666666666666656</v>
+            <v>0.34000000000000008</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -839,10 +840,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>1.6666666666666667</v>
+            <v>2.5</v>
           </cell>
           <cell r="G47">
-            <v>-0.4907407407407407</v>
+            <v>-0.23611111111111116</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -852,6 +853,7 @@
       <sheetData sheetId="3"/>
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1108,11 +1110,11 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1267.6666666666667</v>
+        <v>1243</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>0.13331707845687046</v>
+        <v>0.11126462938881665</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
@@ -1137,11 +1139,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>107.66666666666667</v>
+        <v>106.25</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.38114674441205065</v>
+        <v>0.36297376093294464</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1166,11 +1168,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>434.66666666666669</v>
+        <v>432.5</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.20608828006088276</v>
+        <v>-0.21004566210045661</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1195,11 +1197,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>132.33333333333334</v>
+        <v>116.75</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.35347900201456706</v>
+        <v>0.19409576940957707</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1224,11 +1226,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>6.666666666666667</v>
+        <v>10.25</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.60036330608537702</v>
+        <v>-0.38555858310626712</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1253,11 +1255,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1381</v>
+        <v>1435</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>6.6484133670317247E-2</v>
+        <v>0.10818590283628193</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1282,11 +1284,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>141.33333333333334</v>
+        <v>139.25</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.15674603174603186</v>
+        <v>0.13969494047619047</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1311,11 +1313,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>345.66666666666669</v>
+        <v>369.25</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.13808241045595127</v>
+        <v>0.2157288237054773</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1340,15 +1342,15 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>661.33333333333337</v>
+        <v>807.75</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>-1.0070493454178431E-3</v>
+        <v>0.220166163141994</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H10">
         <v>1.0900000000000001</v>
@@ -1369,15 +1371,15 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>396.66666666666669</v>
+        <v>454</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>-2.1125444008225802E-2</v>
+        <v>0.12035894559730775</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H11">
         <v>1.0900000000000001</v>
@@ -1398,11 +1400,11 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3322.3333333333335</v>
+        <v>3508.75</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>2.2242113163918553E-2</v>
+        <v>7.9600285310694963E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
@@ -1427,15 +1429,15 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2112.3333333333335</v>
+        <v>2274.5</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>-3.0392811439381218E-2</v>
+        <v>4.4045234518444332E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
@@ -1456,15 +1458,15 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2099.3333333333335</v>
+        <v>2225.25</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>-2.9230424303570368E-2</v>
+        <v>2.8995712123759843E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1485,11 +1487,11 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2440.6666666666665</v>
+        <v>2504.75</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>1.4964494767152559E-2</v>
+        <v>4.1613897132487754E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
@@ -1514,11 +1516,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>71</v>
+        <v>73.5</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.46671218846022533</v>
+        <v>-0.44793444861727549</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1543,15 +1545,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>207.66666666666666</v>
+        <v>230.5</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>-8.0566176963842606E-2</v>
+        <v>2.0527269068222997E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1572,11 +1574,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>131.66666666666666</v>
+        <v>131.5</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.10981356279450938</v>
+        <v>-0.11094038106945292</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1601,11 +1603,11 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>525.33333333333337</v>
+        <v>519.25</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>7.9620115210960796E-2</v>
+        <v>6.7118169079869228E-2</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
@@ -1630,11 +1632,11 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>811.66666666666663</v>
+        <v>805.25</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>1.9157962825561592E-2</v>
+        <v>1.1100964556817638E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
@@ -1688,11 +1690,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>63.333333333333336</v>
+        <v>50.5</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>0.28773875539125093</v>
+        <v>2.6802218114602594E-2</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1717,11 +1719,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>605.66666666666663</v>
+        <v>620.5</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-0.11546291379005147</v>
+        <v>-9.3799787573021765E-2</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1746,11 +1748,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>850</v>
+        <v>955</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.23395190692720491</v>
+        <v>-0.13932243660644783</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1775,11 +1777,11 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>576.33333333333337</v>
+        <v>548.25</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>0.19346134538152615</v>
+        <v>0.13530685240963858</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
@@ -1804,11 +1806,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>295</v>
+        <v>348.5</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-0.194888971591614</v>
+        <v>-4.8877310507381311E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1833,11 +1835,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>131.33333333333334</v>
+        <v>127</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.22689313517339005</v>
+        <v>0.18641188959660293</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1862,11 +1864,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>75</v>
+        <v>104.75</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.38798219584569738</v>
+        <v>-0.14521513353115723</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1891,11 +1893,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>440.33333333333331</v>
+        <v>391</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.44312868858741472</v>
+        <v>-0.50551851000229941</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1920,15 +1922,15 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>630</v>
+        <v>683.25</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>-3.3068229384679682E-2</v>
+        <v>4.8660527417329513E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>BAJO</v>
+        <v>SUBIÓ</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1949,11 +1951,11 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>866.33333333333337</v>
+        <v>885</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>2.8122415219189456E-2</v>
+        <v>5.0275110583666072E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
@@ -1978,11 +1980,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>565</v>
+        <v>544.5</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-1.2865311308767446E-2</v>
+        <v>-4.8681702668360916E-2</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2007,11 +2009,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>49.333333333333336</v>
+        <v>42</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.76789278585685772</v>
+        <v>-0.80239520958083832</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2036,11 +2038,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>638</v>
+        <v>693</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.189020586400499</v>
+        <v>1.3777292576419216</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2065,11 +2067,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>163.66666666666666</v>
+        <v>159</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.56265435847605172</v>
+        <v>-0.57512449896756956</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2094,11 +2096,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>312.33333333333331</v>
+        <v>300</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>0.1442686650013878</v>
+        <v>9.9084096586178338E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2123,11 +2125,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>689</v>
+        <v>627.25</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.63887987890582765</v>
+        <v>0.49199913504162596</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2152,11 +2154,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>373.66666666666669</v>
+        <v>336.75</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.51616869543833754</v>
+        <v>0.3663777203983769</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2181,11 +2183,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>237.33333333333334</v>
+        <v>255.25</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-9.899338510209954E-2</v>
+        <v>-3.0974978429680888E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2210,11 +2212,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>49.333333333333336</v>
+        <v>47.25</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-1.1536126290224602E-2</v>
+        <v>-5.3278688524590168E-2</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2239,11 +2241,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>117.66666666666667</v>
+        <v>99.75</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.48177828658652944</v>
+        <v>0.25615340583858037</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2268,11 +2270,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>95</v>
+        <v>80.5</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>1.7718832891246685</v>
+        <v>1.3488063660477452</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2297,11 +2299,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>55</v>
+        <v>50.25</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.46666666666666656</v>
+        <v>0.34000000000000008</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2355,11 +2357,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>1.6666666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.4907407407407407</v>
+        <v>-0.23611111111111116</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>

--- a/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
+++ b/Comparación de Venta Diaria por SKU (Julio vs Agosto).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Orbit\Desktop\Mi_Dashboard_Ventas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50AD65E-4D11-4ED0-B390-6B7CE65E64BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{257639EF-80E3-4CCD-83D9-10B46D84FE01}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -360,6 +360,7 @@
       <sheetName val="INVENTARIO NACIONAL 05-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 06-08-26"/>
       <sheetName val="INVENTARIO NACIONAL 07-08-26"/>
+      <sheetName val="INVENTARIO NACIONAL 10-08-26"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -367,21 +368,21 @@
       <sheetData sheetId="2">
         <row r="4">
           <cell r="F4">
-            <v>1243</v>
+            <v>1114.5999999999999</v>
           </cell>
           <cell r="G4">
-            <v>0.11126462938881665</v>
+            <v>-3.5273081924578342E-3</v>
           </cell>
           <cell r="H4" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="5">
           <cell r="F5">
-            <v>106.25</v>
+            <v>93.8</v>
           </cell>
           <cell r="G5">
-            <v>0.36297376093294464</v>
+            <v>0.20326530612244897</v>
           </cell>
           <cell r="H5" t="str">
             <v>SUBIÓ</v>
@@ -389,10 +390,10 @@
         </row>
         <row r="6">
           <cell r="F6">
-            <v>432.5</v>
+            <v>393.8</v>
           </cell>
           <cell r="G6">
-            <v>-0.21004566210045661</v>
+            <v>-0.2807305936073059</v>
           </cell>
           <cell r="H6" t="str">
             <v>BAJO</v>
@@ -400,10 +401,10 @@
         </row>
         <row r="7">
           <cell r="F7">
-            <v>116.75</v>
+            <v>104.6</v>
           </cell>
           <cell r="G7">
-            <v>0.19409576940957707</v>
+            <v>6.9827986982798684E-2</v>
           </cell>
           <cell r="H7" t="str">
             <v>SUBIÓ</v>
@@ -411,10 +412,10 @@
         </row>
         <row r="8">
           <cell r="F8">
-            <v>10.25</v>
+            <v>8.4</v>
           </cell>
           <cell r="G8">
-            <v>-0.38555858310626712</v>
+            <v>-0.49645776566757494</v>
           </cell>
           <cell r="H8" t="str">
             <v>BAJO</v>
@@ -422,10 +423,10 @@
         </row>
         <row r="9">
           <cell r="F9">
-            <v>1435</v>
+            <v>1301.2</v>
           </cell>
           <cell r="G9">
-            <v>0.10818590283628193</v>
+            <v>4.8581859028362651E-3</v>
           </cell>
           <cell r="H9" t="str">
             <v>SUBIÓ</v>
@@ -433,10 +434,10 @@
         </row>
         <row r="10">
           <cell r="F10">
-            <v>139.25</v>
+            <v>123.4</v>
           </cell>
           <cell r="G10">
-            <v>0.13969494047619047</v>
+            <v>9.9702380952380043E-3</v>
           </cell>
           <cell r="H10" t="str">
             <v>SUBIÓ</v>
@@ -444,10 +445,10 @@
         </row>
         <row r="11">
           <cell r="F11">
-            <v>369.25</v>
+            <v>327</v>
           </cell>
           <cell r="G11">
-            <v>0.2157288237054773</v>
+            <v>7.6623765339718597E-2</v>
           </cell>
           <cell r="H11" t="str">
             <v>SUBIÓ</v>
@@ -455,10 +456,10 @@
         </row>
         <row r="12">
           <cell r="F12">
-            <v>807.75</v>
+            <v>745.6</v>
           </cell>
           <cell r="G12">
-            <v>0.220166163141994</v>
+            <v>0.12628398791540785</v>
           </cell>
           <cell r="H12" t="str">
             <v>SUBIÓ</v>
@@ -466,10 +467,10 @@
         </row>
         <row r="13">
           <cell r="F13">
-            <v>454</v>
+            <v>423.2</v>
           </cell>
           <cell r="G13">
-            <v>0.12035894559730775</v>
+            <v>4.4352215367358339E-2</v>
           </cell>
           <cell r="H13" t="str">
             <v>SUBIÓ</v>
@@ -477,54 +478,54 @@
         </row>
         <row r="14">
           <cell r="F14">
-            <v>3508.75</v>
+            <v>3133.8</v>
           </cell>
           <cell r="G14">
-            <v>7.9600285310694963E-2</v>
+            <v>-3.5767331925427581E-2</v>
           </cell>
           <cell r="H14" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="15">
           <cell r="F15">
-            <v>2274.5</v>
+            <v>2087.4</v>
           </cell>
           <cell r="G15">
-            <v>4.4045234518444332E-2</v>
+            <v>-4.1837756634952372E-2</v>
           </cell>
           <cell r="H15" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="16">
           <cell r="F16">
-            <v>2225.25</v>
+            <v>2021</v>
           </cell>
           <cell r="G16">
-            <v>2.8995712123759843E-2</v>
+            <v>-6.5453169665377509E-2</v>
           </cell>
           <cell r="H16" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="17">
           <cell r="F17">
-            <v>2504.75</v>
+            <v>2275.8000000000002</v>
           </cell>
           <cell r="G17">
-            <v>4.1613897132487754E-2</v>
+            <v>-5.3596204374042888E-2</v>
           </cell>
           <cell r="H17" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="18">
           <cell r="F18">
-            <v>73.5</v>
+            <v>62</v>
           </cell>
           <cell r="G18">
-            <v>-0.44793444861727549</v>
+            <v>-0.53431205189484454</v>
           </cell>
           <cell r="H18" t="str">
             <v>BAJO</v>
@@ -532,21 +533,21 @@
         </row>
         <row r="19">
           <cell r="F19">
-            <v>230.5</v>
+            <v>208.2</v>
           </cell>
           <cell r="G19">
-            <v>2.0527269068222997E-2</v>
+            <v>-7.8204870195210385E-2</v>
           </cell>
           <cell r="H19" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="20">
           <cell r="F20">
-            <v>131.5</v>
+            <v>125.6</v>
           </cell>
           <cell r="G20">
-            <v>-0.11094038106945292</v>
+            <v>-0.15082974800245852</v>
           </cell>
           <cell r="H20" t="str">
             <v>BAJO</v>
@@ -554,24 +555,24 @@
         </row>
         <row r="21">
           <cell r="F21">
-            <v>519.25</v>
+            <v>484.4</v>
           </cell>
           <cell r="G21">
-            <v>6.7118169079869228E-2</v>
+            <v>-4.5025688930406815E-3</v>
           </cell>
           <cell r="H21" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="22">
           <cell r="F22">
-            <v>805.25</v>
+            <v>731</v>
           </cell>
           <cell r="G22">
-            <v>1.1100964556817638E-2</v>
+            <v>-8.2130015410079249E-2</v>
           </cell>
           <cell r="H22" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="23">
@@ -587,10 +588,10 @@
         </row>
         <row r="24">
           <cell r="F24">
-            <v>50.5</v>
+            <v>80.400000000000006</v>
           </cell>
           <cell r="G24">
-            <v>2.6802218114602594E-2</v>
+            <v>0.63475046210720909</v>
           </cell>
           <cell r="H24" t="str">
             <v>SUBIÓ</v>
@@ -598,10 +599,10 @@
         </row>
         <row r="25">
           <cell r="F25">
-            <v>620.5</v>
+            <v>575.4</v>
           </cell>
           <cell r="G25">
-            <v>-9.3799787573021765E-2</v>
+            <v>-0.15966542750929369</v>
           </cell>
           <cell r="H25" t="str">
             <v>BAJO</v>
@@ -609,10 +610,10 @@
         </row>
         <row r="26">
           <cell r="F26">
-            <v>955</v>
+            <v>882.6</v>
           </cell>
           <cell r="G26">
-            <v>-0.13932243660644783</v>
+            <v>-0.20457170947523651</v>
           </cell>
           <cell r="H26" t="str">
             <v>BAJO</v>
@@ -620,21 +621,21 @@
         </row>
         <row r="27">
           <cell r="F27">
-            <v>548.25</v>
+            <v>480.2</v>
           </cell>
           <cell r="G27">
-            <v>0.13530685240963858</v>
+            <v>-5.609939759036231E-3</v>
           </cell>
           <cell r="H27" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="28">
           <cell r="F28">
-            <v>348.5</v>
+            <v>331.6</v>
           </cell>
           <cell r="G28">
-            <v>-4.8877310507381311E-2</v>
+            <v>-9.5000620270437874E-2</v>
           </cell>
           <cell r="H28" t="str">
             <v>BAJO</v>
@@ -642,10 +643,10 @@
         </row>
         <row r="29">
           <cell r="F29">
-            <v>127</v>
+            <v>116.4</v>
           </cell>
           <cell r="G29">
-            <v>0.18641188959660293</v>
+            <v>8.738853503184707E-2</v>
           </cell>
           <cell r="H29" t="str">
             <v>SUBIÓ</v>
@@ -653,10 +654,10 @@
         </row>
         <row r="30">
           <cell r="F30">
-            <v>104.75</v>
+            <v>102.6</v>
           </cell>
           <cell r="G30">
-            <v>-0.14521513353115723</v>
+            <v>-0.162759643916914</v>
           </cell>
           <cell r="H30" t="str">
             <v>BAJO</v>
@@ -664,10 +665,10 @@
         </row>
         <row r="31">
           <cell r="F31">
-            <v>391</v>
+            <v>406.4</v>
           </cell>
           <cell r="G31">
-            <v>-0.50551851000229941</v>
+            <v>-0.48604276845251781</v>
           </cell>
           <cell r="H31" t="str">
             <v>BAJO</v>
@@ -675,32 +676,32 @@
         </row>
         <row r="32">
           <cell r="F32">
-            <v>683.25</v>
+            <v>631.6</v>
           </cell>
           <cell r="G32">
-            <v>4.8660527417329513E-2</v>
+            <v>-3.0612529649783671E-2</v>
           </cell>
           <cell r="H32" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="33">
           <cell r="F33">
-            <v>885</v>
+            <v>820</v>
           </cell>
           <cell r="G33">
-            <v>5.0275110583666072E-2</v>
+            <v>-2.6863739346207782E-2</v>
           </cell>
           <cell r="H33" t="str">
-            <v>SUBIÓ</v>
+            <v>BAJO</v>
           </cell>
         </row>
         <row r="34">
           <cell r="F34">
-            <v>544.5</v>
+            <v>494.6</v>
           </cell>
           <cell r="G34">
-            <v>-4.8681702668360916E-2</v>
+            <v>-0.13586404066073698</v>
           </cell>
           <cell r="H34" t="str">
             <v>BAJO</v>
@@ -708,10 +709,10 @@
         </row>
         <row r="35">
           <cell r="F35">
-            <v>42</v>
+            <v>34.4</v>
           </cell>
           <cell r="G35">
-            <v>-0.80239520958083832</v>
+            <v>-0.83815226689478184</v>
           </cell>
           <cell r="H35" t="str">
             <v>BAJO</v>
@@ -719,10 +720,10 @@
         </row>
         <row r="36">
           <cell r="F36">
-            <v>693</v>
+            <v>647.4</v>
           </cell>
           <cell r="G36">
-            <v>1.3777292576419216</v>
+            <v>1.2212726138490333</v>
           </cell>
           <cell r="H36" t="str">
             <v>SUBIÓ</v>
@@ -730,10 +731,10 @@
         </row>
         <row r="37">
           <cell r="F37">
-            <v>159</v>
+            <v>132.4</v>
           </cell>
           <cell r="G37">
-            <v>-0.57512449896756956</v>
+            <v>-0.64620429976922145</v>
           </cell>
           <cell r="H37" t="str">
             <v>BAJO</v>
@@ -741,10 +742,10 @@
         </row>
         <row r="38">
           <cell r="F38">
-            <v>300</v>
+            <v>285.60000000000002</v>
           </cell>
           <cell r="G38">
-            <v>9.9084096586178338E-2</v>
+            <v>4.6328059950041744E-2</v>
           </cell>
           <cell r="H38" t="str">
             <v>SUBIÓ</v>
@@ -752,10 +753,10 @@
         </row>
         <row r="39">
           <cell r="F39">
-            <v>627.25</v>
+            <v>574.79999999999995</v>
           </cell>
           <cell r="G39">
-            <v>0.49199913504162596</v>
+            <v>0.36723970158936092</v>
           </cell>
           <cell r="H39" t="str">
             <v>SUBIÓ</v>
@@ -763,10 +764,10 @@
         </row>
         <row r="40">
           <cell r="F40">
-            <v>336.75</v>
+            <v>312.2</v>
           </cell>
           <cell r="G40">
-            <v>0.3663777203983769</v>
+            <v>0.26676503135374396</v>
           </cell>
           <cell r="H40" t="str">
             <v>SUBIÓ</v>
@@ -774,10 +775,10 @@
         </row>
         <row r="41">
           <cell r="F41">
-            <v>255.25</v>
+            <v>250.4</v>
           </cell>
           <cell r="G41">
-            <v>-3.0974978429680888E-2</v>
+            <v>-4.9387402933563473E-2</v>
           </cell>
           <cell r="H41" t="str">
             <v>BAJO</v>
@@ -785,10 +786,10 @@
         </row>
         <row r="42">
           <cell r="F42">
-            <v>47.25</v>
+            <v>41</v>
           </cell>
           <cell r="G42">
-            <v>-5.3278688524590168E-2</v>
+            <v>-0.17850637522768664</v>
           </cell>
           <cell r="H42" t="str">
             <v>BAJO</v>
@@ -796,10 +797,10 @@
         </row>
         <row r="43">
           <cell r="F43">
-            <v>99.75</v>
+            <v>90.4</v>
           </cell>
           <cell r="G43">
-            <v>0.25615340583858037</v>
+            <v>0.13840870062965105</v>
           </cell>
           <cell r="H43" t="str">
             <v>SUBIÓ</v>
@@ -807,10 +808,10 @@
         </row>
         <row r="44">
           <cell r="F44">
-            <v>80.5</v>
+            <v>66.2</v>
           </cell>
           <cell r="G44">
-            <v>1.3488063660477452</v>
+            <v>0.93156498673740051</v>
           </cell>
           <cell r="H44" t="str">
             <v>SUBIÓ</v>
@@ -818,10 +819,10 @@
         </row>
         <row r="45">
           <cell r="F45">
-            <v>50.25</v>
+            <v>43.2</v>
           </cell>
           <cell r="G45">
-            <v>0.34000000000000008</v>
+            <v>0.15200000000000014</v>
           </cell>
           <cell r="H45" t="str">
             <v>SUBIÓ</v>
@@ -840,10 +841,10 @@
         </row>
         <row r="47">
           <cell r="F47">
-            <v>2.5</v>
+            <v>2</v>
           </cell>
           <cell r="G47">
-            <v>-0.23611111111111116</v>
+            <v>-0.38888888888888895</v>
           </cell>
           <cell r="H47" t="str">
             <v>BAJO</v>
@@ -854,6 +855,7 @@
       <sheetData sheetId="4"/>
       <sheetData sheetId="5"/>
       <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
@@ -1110,15 +1112,15 @@
       </c>
       <c r="E2" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F4</f>
-        <v>1243</v>
+        <v>1114.5999999999999</v>
       </c>
       <c r="F2" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G4</f>
-        <v>0.11126462938881665</v>
+        <v>-3.5273081924578342E-3</v>
       </c>
       <c r="G2" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H4</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H2">
         <v>1.36</v>
@@ -1139,11 +1141,11 @@
       </c>
       <c r="E3" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F5</f>
-        <v>106.25</v>
+        <v>93.8</v>
       </c>
       <c r="F3" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G5</f>
-        <v>0.36297376093294464</v>
+        <v>0.20326530612244897</v>
       </c>
       <c r="G3" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H5</f>
@@ -1168,11 +1170,11 @@
       </c>
       <c r="E4" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F6</f>
-        <v>432.5</v>
+        <v>393.8</v>
       </c>
       <c r="F4" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G6</f>
-        <v>-0.21004566210045661</v>
+        <v>-0.2807305936073059</v>
       </c>
       <c r="G4" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H6</f>
@@ -1197,11 +1199,11 @@
       </c>
       <c r="E5" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F7</f>
-        <v>116.75</v>
+        <v>104.6</v>
       </c>
       <c r="F5" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G7</f>
-        <v>0.19409576940957707</v>
+        <v>6.9827986982798684E-2</v>
       </c>
       <c r="G5" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H7</f>
@@ -1226,11 +1228,11 @@
       </c>
       <c r="E6" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F8</f>
-        <v>10.25</v>
+        <v>8.4</v>
       </c>
       <c r="F6" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G8</f>
-        <v>-0.38555858310626712</v>
+        <v>-0.49645776566757494</v>
       </c>
       <c r="G6" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H8</f>
@@ -1255,11 +1257,11 @@
       </c>
       <c r="E7" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F9</f>
-        <v>1435</v>
+        <v>1301.2</v>
       </c>
       <c r="F7" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G9</f>
-        <v>0.10818590283628193</v>
+        <v>4.8581859028362651E-3</v>
       </c>
       <c r="G7" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H9</f>
@@ -1284,11 +1286,11 @@
       </c>
       <c r="E8" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F10</f>
-        <v>139.25</v>
+        <v>123.4</v>
       </c>
       <c r="F8" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G10</f>
-        <v>0.13969494047619047</v>
+        <v>9.9702380952380043E-3</v>
       </c>
       <c r="G8" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H10</f>
@@ -1313,11 +1315,11 @@
       </c>
       <c r="E9" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F11</f>
-        <v>369.25</v>
+        <v>327</v>
       </c>
       <c r="F9" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G11</f>
-        <v>0.2157288237054773</v>
+        <v>7.6623765339718597E-2</v>
       </c>
       <c r="G9" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H11</f>
@@ -1342,11 +1344,11 @@
       </c>
       <c r="E10" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F12</f>
-        <v>807.75</v>
+        <v>745.6</v>
       </c>
       <c r="F10" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G12</f>
-        <v>0.220166163141994</v>
+        <v>0.12628398791540785</v>
       </c>
       <c r="G10" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H12</f>
@@ -1371,11 +1373,11 @@
       </c>
       <c r="E11" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F13</f>
-        <v>454</v>
+        <v>423.2</v>
       </c>
       <c r="F11" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G13</f>
-        <v>0.12035894559730775</v>
+        <v>4.4352215367358339E-2</v>
       </c>
       <c r="G11" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H13</f>
@@ -1400,15 +1402,15 @@
       </c>
       <c r="E12" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F14</f>
-        <v>3508.75</v>
+        <v>3133.8</v>
       </c>
       <c r="F12" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G14</f>
-        <v>7.9600285310694963E-2</v>
+        <v>-3.5767331925427581E-2</v>
       </c>
       <c r="G12" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H14</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H12">
         <v>1.1599999999999999</v>
@@ -1429,15 +1431,15 @@
       </c>
       <c r="E13" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F15</f>
-        <v>2274.5</v>
+        <v>2087.4</v>
       </c>
       <c r="F13" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G15</f>
-        <v>4.4045234518444332E-2</v>
+        <v>-4.1837756634952372E-2</v>
       </c>
       <c r="G13" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H15</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H13">
         <v>1.1599999999999999</v>
@@ -1458,15 +1460,15 @@
       </c>
       <c r="E14" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F16</f>
-        <v>2225.25</v>
+        <v>2021</v>
       </c>
       <c r="F14" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G16</f>
-        <v>2.8995712123759843E-2</v>
+        <v>-6.5453169665377509E-2</v>
       </c>
       <c r="G14" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H16</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H14">
         <v>1.1599999999999999</v>
@@ -1487,15 +1489,15 @@
       </c>
       <c r="E15" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F17</f>
-        <v>2504.75</v>
+        <v>2275.8000000000002</v>
       </c>
       <c r="F15" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G17</f>
-        <v>4.1613897132487754E-2</v>
+        <v>-5.3596204374042888E-2</v>
       </c>
       <c r="G15" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H17</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H15">
         <v>1.1599999999999999</v>
@@ -1516,11 +1518,11 @@
       </c>
       <c r="E16" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F18</f>
-        <v>73.5</v>
+        <v>62</v>
       </c>
       <c r="F16" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G18</f>
-        <v>-0.44793444861727549</v>
+        <v>-0.53431205189484454</v>
       </c>
       <c r="G16" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H18</f>
@@ -1545,15 +1547,15 @@
       </c>
       <c r="E17" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F19</f>
-        <v>230.5</v>
+        <v>208.2</v>
       </c>
       <c r="F17" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G19</f>
-        <v>2.0527269068222997E-2</v>
+        <v>-7.8204870195210385E-2</v>
       </c>
       <c r="G17" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H19</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H17">
         <v>3.68</v>
@@ -1574,11 +1576,11 @@
       </c>
       <c r="E18" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F20</f>
-        <v>131.5</v>
+        <v>125.6</v>
       </c>
       <c r="F18" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G20</f>
-        <v>-0.11094038106945292</v>
+        <v>-0.15082974800245852</v>
       </c>
       <c r="G18" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H20</f>
@@ -1603,15 +1605,15 @@
       </c>
       <c r="E19" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F21</f>
-        <v>519.25</v>
+        <v>484.4</v>
       </c>
       <c r="F19" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G21</f>
-        <v>6.7118169079869228E-2</v>
+        <v>-4.5025688930406815E-3</v>
       </c>
       <c r="G19" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H21</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H19">
         <v>4.1500000000000004</v>
@@ -1632,15 +1634,15 @@
       </c>
       <c r="E20" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F22</f>
-        <v>805.25</v>
+        <v>731</v>
       </c>
       <c r="F20" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G22</f>
-        <v>1.1100964556817638E-2</v>
+        <v>-8.2130015410079249E-2</v>
       </c>
       <c r="G20" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H22</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H20">
         <v>4.1500000000000004</v>
@@ -1690,11 +1692,11 @@
       </c>
       <c r="E22" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F24</f>
-        <v>50.5</v>
+        <v>80.400000000000006</v>
       </c>
       <c r="F22" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G24</f>
-        <v>2.6802218114602594E-2</v>
+        <v>0.63475046210720909</v>
       </c>
       <c r="G22" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H24</f>
@@ -1719,11 +1721,11 @@
       </c>
       <c r="E23" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F25</f>
-        <v>620.5</v>
+        <v>575.4</v>
       </c>
       <c r="F23" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G25</f>
-        <v>-9.3799787573021765E-2</v>
+        <v>-0.15966542750929369</v>
       </c>
       <c r="G23" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H25</f>
@@ -1748,11 +1750,11 @@
       </c>
       <c r="E24" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F26</f>
-        <v>955</v>
+        <v>882.6</v>
       </c>
       <c r="F24" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G26</f>
-        <v>-0.13932243660644783</v>
+        <v>-0.20457170947523651</v>
       </c>
       <c r="G24" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H26</f>
@@ -1777,15 +1779,15 @@
       </c>
       <c r="E25" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F27</f>
-        <v>548.25</v>
+        <v>480.2</v>
       </c>
       <c r="F25" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G27</f>
-        <v>0.13530685240963858</v>
+        <v>-5.609939759036231E-3</v>
       </c>
       <c r="G25" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H27</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H25">
         <v>1.63</v>
@@ -1806,11 +1808,11 @@
       </c>
       <c r="E26" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F28</f>
-        <v>348.5</v>
+        <v>331.6</v>
       </c>
       <c r="F26" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G28</f>
-        <v>-4.8877310507381311E-2</v>
+        <v>-9.5000620270437874E-2</v>
       </c>
       <c r="G26" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H28</f>
@@ -1835,11 +1837,11 @@
       </c>
       <c r="E27" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F29</f>
-        <v>127</v>
+        <v>116.4</v>
       </c>
       <c r="F27" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G29</f>
-        <v>0.18641188959660293</v>
+        <v>8.738853503184707E-2</v>
       </c>
       <c r="G27" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H29</f>
@@ -1864,11 +1866,11 @@
       </c>
       <c r="E28" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F30</f>
-        <v>104.75</v>
+        <v>102.6</v>
       </c>
       <c r="F28" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G30</f>
-        <v>-0.14521513353115723</v>
+        <v>-0.162759643916914</v>
       </c>
       <c r="G28" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H30</f>
@@ -1893,11 +1895,11 @@
       </c>
       <c r="E29" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F31</f>
-        <v>391</v>
+        <v>406.4</v>
       </c>
       <c r="F29" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G31</f>
-        <v>-0.50551851000229941</v>
+        <v>-0.48604276845251781</v>
       </c>
       <c r="G29" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H31</f>
@@ -1922,15 +1924,15 @@
       </c>
       <c r="E30" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F32</f>
-        <v>683.25</v>
+        <v>631.6</v>
       </c>
       <c r="F30" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G32</f>
-        <v>4.8660527417329513E-2</v>
+        <v>-3.0612529649783671E-2</v>
       </c>
       <c r="G30" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H32</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H30">
         <v>1.1599999999999999</v>
@@ -1951,15 +1953,15 @@
       </c>
       <c r="E31" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F33</f>
-        <v>885</v>
+        <v>820</v>
       </c>
       <c r="F31" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G33</f>
-        <v>5.0275110583666072E-2</v>
+        <v>-2.6863739346207782E-2</v>
       </c>
       <c r="G31" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H33</f>
-        <v>SUBIÓ</v>
+        <v>BAJO</v>
       </c>
       <c r="H31">
         <v>1.1599999999999999</v>
@@ -1980,11 +1982,11 @@
       </c>
       <c r="E32" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F34</f>
-        <v>544.5</v>
+        <v>494.6</v>
       </c>
       <c r="F32" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G34</f>
-        <v>-4.8681702668360916E-2</v>
+        <v>-0.13586404066073698</v>
       </c>
       <c r="G32" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H34</f>
@@ -2009,11 +2011,11 @@
       </c>
       <c r="E33" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F35</f>
-        <v>42</v>
+        <v>34.4</v>
       </c>
       <c r="F33" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G35</f>
-        <v>-0.80239520958083832</v>
+        <v>-0.83815226689478184</v>
       </c>
       <c r="G33" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H35</f>
@@ -2038,11 +2040,11 @@
       </c>
       <c r="E34" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F36</f>
-        <v>693</v>
+        <v>647.4</v>
       </c>
       <c r="F34" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G36</f>
-        <v>1.3777292576419216</v>
+        <v>1.2212726138490333</v>
       </c>
       <c r="G34" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H36</f>
@@ -2067,11 +2069,11 @@
       </c>
       <c r="E35" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F37</f>
-        <v>159</v>
+        <v>132.4</v>
       </c>
       <c r="F35" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G37</f>
-        <v>-0.57512449896756956</v>
+        <v>-0.64620429976922145</v>
       </c>
       <c r="G35" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H37</f>
@@ -2096,11 +2098,11 @@
       </c>
       <c r="E36" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F38</f>
-        <v>300</v>
+        <v>285.60000000000002</v>
       </c>
       <c r="F36" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G38</f>
-        <v>9.9084096586178338E-2</v>
+        <v>4.6328059950041744E-2</v>
       </c>
       <c r="G36" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H38</f>
@@ -2125,11 +2127,11 @@
       </c>
       <c r="E37" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F39</f>
-        <v>627.25</v>
+        <v>574.79999999999995</v>
       </c>
       <c r="F37" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G39</f>
-        <v>0.49199913504162596</v>
+        <v>0.36723970158936092</v>
       </c>
       <c r="G37" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H39</f>
@@ -2154,11 +2156,11 @@
       </c>
       <c r="E38" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F40</f>
-        <v>336.75</v>
+        <v>312.2</v>
       </c>
       <c r="F38" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G40</f>
-        <v>0.3663777203983769</v>
+        <v>0.26676503135374396</v>
       </c>
       <c r="G38" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H40</f>
@@ -2183,11 +2185,11 @@
       </c>
       <c r="E39" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F41</f>
-        <v>255.25</v>
+        <v>250.4</v>
       </c>
       <c r="F39" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G41</f>
-        <v>-3.0974978429680888E-2</v>
+        <v>-4.9387402933563473E-2</v>
       </c>
       <c r="G39" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H41</f>
@@ -2212,11 +2214,11 @@
       </c>
       <c r="E40" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F42</f>
-        <v>47.25</v>
+        <v>41</v>
       </c>
       <c r="F40" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G42</f>
-        <v>-5.3278688524590168E-2</v>
+        <v>-0.17850637522768664</v>
       </c>
       <c r="G40" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H42</f>
@@ -2241,11 +2243,11 @@
       </c>
       <c r="E41" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F43</f>
-        <v>99.75</v>
+        <v>90.4</v>
       </c>
       <c r="F41" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G43</f>
-        <v>0.25615340583858037</v>
+        <v>0.13840870062965105</v>
       </c>
       <c r="G41" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H43</f>
@@ -2270,11 +2272,11 @@
       </c>
       <c r="E42" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F44</f>
-        <v>80.5</v>
+        <v>66.2</v>
       </c>
       <c r="F42" s="6">
         <f ca="1">'[1]DESV. VTS BY SKU'!G44</f>
-        <v>1.3488063660477452</v>
+        <v>0.93156498673740051</v>
       </c>
       <c r="G42" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H44</f>
@@ -2299,11 +2301,11 @@
       </c>
       <c r="E43" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F45</f>
-        <v>50.25</v>
+        <v>43.2</v>
       </c>
       <c r="F43" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G45</f>
-        <v>0.34000000000000008</v>
+        <v>0.15200000000000014</v>
       </c>
       <c r="G43" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H45</f>
@@ -2357,11 +2359,11 @@
       </c>
       <c r="E45" s="5">
         <f ca="1">'[1]DESV. VTS BY SKU'!F47</f>
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="F45" s="7">
         <f ca="1">'[1]DESV. VTS BY SKU'!G47</f>
-        <v>-0.23611111111111116</v>
+        <v>-0.38888888888888895</v>
       </c>
       <c r="G45" s="8" t="str">
         <f ca="1">'[1]DESV. VTS BY SKU'!H47</f>
